--- a/clients.xlsx
+++ b/clients.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Data Copilot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4997061F-F0F0-44FD-ADD6-413100EF8A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DAA19F-4320-4D65-A908-05DA843BCB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{52930DBB-3838-46AD-B41E-F61A60DE6A8B}"/>
   </bookViews>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>client_id</t>
   </si>
@@ -59,6 +58,9 @@
   </si>
   <si>
     <t>Omar</t>
+  </si>
+  <si>
+    <t>montant</t>
   </si>
 </sst>
 </file>
@@ -424,10 +426,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E481FBF-C4E4-4437-B12B-9D96F7CF4EAF}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -437,8 +439,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -448,8 +453,11 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="D2">
+        <v>3.7</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -459,8 +467,11 @@
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D3">
+        <v>5.9</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -468,6 +479,9 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>4</v>
       </c>
     </row>
